--- a/content/src-assets/data/Матч Тура/Матч Тура 26-27.xlsx
+++ b/content/src-assets/data/Матч Тура/Матч Тура 26-27.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-180" yWindow="-180" windowWidth="29160" windowHeight="15960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-180" yWindow="-180" windowWidth="29160" windowHeight="15960" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="mt_cska_baltika" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mt_spartak_krasnodar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mt_zenit_dinmos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mt_cska_loko" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,18 +22,15 @@
   <fonts count="3">
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -78,16 +77,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -96,7 +89,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -243,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -277,6 +271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -311,20 +306,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -446,7 +437,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -457,124 +487,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col width="76.42578125" customWidth="1" min="2" max="2"/>
-    <col width="17.5703125" customWidth="1" min="3" max="3"/>
-    <col width="43.28515625" customWidth="1" min="4" max="4"/>
-    <col width="18.140625" customWidth="1" min="5" max="5"/>
-    <col width="14.140625" customWidth="1" min="6" max="6"/>
-    <col width="19.5703125" customWidth="1" min="7" max="7"/>
-    <col width="12.5703125" customWidth="1" min="8" max="8"/>
-    <col width="21.42578125" customWidth="1" min="9" max="9"/>
-    <col width="13.5703125" customWidth="1" min="10" max="10"/>
-    <col width="20.5703125" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="19.7109375" customWidth="1" min="13" max="13"/>
-    <col width="14.140625" customWidth="1" min="14" max="14"/>
-    <col width="21.5703125" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="18.140625" customWidth="1" min="17" max="17"/>
-  </cols>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>textQue</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>slugQue</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>slugDlg</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>slugCorAns</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>txtCorAns</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>wrSlgAns1</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>wrTxtAns1</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>wrSlgAns2</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>wrTxtAns2</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>wrSlgAns3</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>wrTxtAns3</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>wrSlgAns4</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>wrTxtAns4</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>wrSlgAns5</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>wrTxtAns5</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>__EMPTY</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>__EMPTY_1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>__EMPTY_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Кто этот футболист?</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>cska_oblyakov</t>
         </is>
@@ -584,230 +613,74 @@
           <t>28-летний (05.01.1998) российский центральный хавбек. Пришёл из «Уфы» в августе 2018 за €4 млн и давно закрепился в старте</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>cska_oblyakov</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>cska_oblyakov</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Иван Обляков</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>cska_akinfeev</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Игорь Акинфеев</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>cska_torop</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Владислав Тороп</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>cska_krugovoy</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Данил Круговой</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>cska_glebov</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Кирилл Глебов</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>cska_shumanskiy</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Артем Шуманский</t>
         </is>
       </c>
-      <c r="R2" s="1" t="n"/>
-      <c r="S2" s="1" t="n"/>
-      <c r="T2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -818,92 +691,4885 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>textQue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>slugQue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>slugDlg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>slugCorAns</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>txtCorAns</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>wrSlgAns1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>wrTxtAns1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wrSlgAns2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>wrTxtAns2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wrSlgAns3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>wrTxtAns3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>wrSlgAns4</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>wrTxtAns4</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>wrSlgAns5</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>wrTxtAns5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>spartak_djiku</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>spartak_djiku</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Александер Джику</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Манфред Угальде</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Кристофер Мартинс</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Эсекьель Барко</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Пабло Солари</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Тео Бонгонда</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>spartak_parada</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>spartak_parada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Виктор Парада</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Рикардо Мангас</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Кристофер Мартинс</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Эсекьель Барко</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Тео Бонгонда</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Хесус Медина</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>spartak_barco</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>27-летний (29.03.1999) аргентинский атакующий полузащитник. Перешёл 25 июля 2024 из «Ривер Плейт» за ≈ €8 млн</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>spartak_barco</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Эсекьель Барко</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Рикардо Мангас</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Кристофер Мартинс</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Пабло Солари</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Манфред Угальде</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Хесус Медина</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>spartak_daku</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>spartak_daku</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Мирлинд Даку</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Кристофер Ву</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Кристофер Мартинс</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Жедсон Фернандеш</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Пабло Солари</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Срджан Бабич</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Какого футболиста Спартака дисквалифицировали из-за содержания в крови бромантана?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2003 год</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>spartak_titov</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Егор Титов</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Илья Цымбаларь</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Андрей Тихонов</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Вадим Евсеев</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Александр Филимонов</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Дмитрий Хлестов</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Какой бывший главный тренер Спартака вывел Швейцарию в 1/4 на ЧМ-2026?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2014—2015 года</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Мурат Якин</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Унаи Эмери</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Руй Витория</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Массимо Каррера </t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Невио Скала</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Рауль Рианчо </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Каким было последнее название Спартака до 1934 года?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Промкооперация</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Пищевики</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Дукат</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Красная Пресня</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>РГО Сокол</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Московский клуб спорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Как зовут главного тренера Спартака?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>spartak_carsedo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Главный тренер</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>spartak_carsedo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Хуан Карседо</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Владимир Слишкович</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Доменико Тедеско</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Димитр Димитров</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Владимир Вайсс</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Миодраг Божович</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>krasnodar_costa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27-летний (21.07.1999) бразильский центральный защитник</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>krasnodar_costa</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Диего Коста</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Витор Тормена</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Джубал</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Джованни Гонсалес</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Лукас Олаза</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Кевин Ленини</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>krasnodar_batxi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28-летний (01.05.1998) ангольский полузащитник</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>krasnodar_batxi</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Батчи</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Диего Коста</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Витор Тормена</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Джубал</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Лукас Олаза</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Джованни Гонсалес</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>krasnodar_lenini</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>29-летний (27.01.1997) кабо-вердианский опорный полузащитник</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>krasnodar_lenini</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Кевин Ленини</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Диего Коста</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Витор Тормена</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Джубал</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Лукас Олаза</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Джованни Гонсалес</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>krasnodar_petrov</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>35-летний (02.01.1991) российский правый защитник. В клубе с января 2013</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>krasnodar_petrov</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Сергей Петров</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Станислав Агкацев</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Александр Корякин</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Даниил Голиков</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Роман Сафронов</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Дмитрий Кучугура</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Какой тренер вывел Краснодар в РПЛ впервые в истории?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>В 2010 году ФК Сатурн подал заявление о выходе из премьер-лиги и на его место был взят, занявщий 5-е место ФК Краснодар. Сергей Ташуев к тому времени уже не работал.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Сергей Ташуев</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Павел Садырин</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Виктор Гончаренко</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Мурад Мусаев</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Александр Кузнецов</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Олег Кононов</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Какое животное является талисманом Краснодара?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Талисманом Краснодара является бык, который также размещён на эмблеме клуба</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mas_krasnodar</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Бык</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Конь</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Лев</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Журавль</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Дракон</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Волк</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Кто является рекордсменом Краснодара по количеству проведенных игр во всех турнирах?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>На счету Сергея Петрова 304 матча в футболке Краснодара</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>krasnodar_petrov</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Сергей Петров</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Матвей Сафонов</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Александр Мартынович</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Жоаозиньо</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Юрий Газинский</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Маурисио Перейра</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Как зовут главного тренера Краснодара?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>krasnodar_musaev</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Главный тренер</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>krasnodar_musaev</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Мурад Мусаев</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Рашид Рахимов</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Магомед Адиев</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Игорь Осинькин</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Александр Тарханов</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Юрий Нагайцев</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>С какой командой играл Спартак в прошлом туре?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ахмат 1:2 Спартак Москва</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>logo_rubin</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Рубин</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Динамо Москва</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>С кем сыграет Спартак в следующем туре?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4 тур. 16.08, 21:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>logo_lokomotiv</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Локомотив</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>logo_ks</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Крылья Советов</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>logo_akron</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Акрон</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>С какой командой играл Краснодар в прошлом туре?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Краснодар 3:2 Факел</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Родина</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>logo_lokomotiv</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Локомотив</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>С кем сыграет Краснодар в следующем туре?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4 тур. 15.08, 22:45</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>logo_orenburg</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Оренбург</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>logo_cska</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>ЦСКА</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>logo_ks</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Крылья Советов</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Кто лидирует в РПЛ после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>logo_rpl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6 очков</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Родина</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>logo_rostov</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>На каком месте находится Спартак после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6 очков</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2 место</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3 место</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6 место</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4 место</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5 место</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1 место</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>На каком месте находится Краснодар после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6 очков</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3 место</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6 место</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2 место</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1 место</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7 место</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5 место</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Какая из команд набрала больше очков в последних 5 матчах?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>logo_rpl</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Спартак: 9 очков, Краснодар: 11 очков</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>logo_akron</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Акрон</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>logo_ks</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Крылья Советов</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>logo_rubin</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Рубин</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Кто чаще побеждал в очных противостояниях, Спартак или Краснодар?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Официальные: победы Спартак — 22, Краснодар — 13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Поровну</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ничья</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Никто</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Затрудняюсь ответить</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>С каким счетом завершилась их последняя встреча?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 1:2 Краснодар</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 2:2 Краснодар</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 1:3 Краснодар</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 0:2 Краснодар</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 1:1 Краснодар</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Спартак Москва 2:1 Краснодар</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>textQue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>slugQue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>slugDlg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>slugCorAns</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>txtCorAns</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>wrSlgAns1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>wrTxtAns1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wrSlgAns2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>wrTxtAns2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>wrSlgAns3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>wrTxtAns3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>wrSlgAns4</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>wrTxtAns4</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>wrSlgAns5</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>wrTxtAns5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>zs_henrique</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>24-летний (02.01.2001) бразильский вингер. Перешёл в Зенит 20.01.2025 из «Ботафого»</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>zs_henrique</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Луис Энрике</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Нино</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Роберт Ренан</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Дуглас Сантос</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Жерсон</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Роман Вега</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>zs_vega</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22-летний (01.01.2004) аргентинский левый защитник. Перешёл в Зенит в июле 2025 из «Архентинос Хуниорс»</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>zs_vega</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Роман Вега</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Педро</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Матео Кассьерра</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Лусиано Гонду</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Дуглас Сантос</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Роберт Ренан</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>zs_erokhin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>35-летний (13.10.1989) российский полузащитник. Перешёл в Зенит 28.06.2017 на правах свободного агента из «Ростова»</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>zs_erokhin</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Александр Ерохин</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Вячеслав Караваев</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Александр Соболев</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Максим Глушенков</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Андрей Мостовой</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Юрий Горшков</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>zs_pedro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19-летний (05.02.2006) бразильский вингер. Перешёл в Зенит 04.01.2024 из «Коринтианса»</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>zs_pedro</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Педро</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Роман Вега</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Матео Кассьерра</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Лусиано Гонду</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Роберт Ренан</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Нино</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Кто забил победный гол в финале Кубка УЕФА 2008 года против «Рейнджерс»?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Первый и победный гол на 72-й минуте забил Игорь Денисов с передачи Андрея Аршавина</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Игорь Денисов</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Константин Зырянов</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Анатолий Тимощук</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Виктор Файзулин</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Фатих Текке</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Андрей Аршавин</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Какое название носил Зенит до 1939 года?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Сталинец</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ленинградец</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Петровский</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Север</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Арсенал</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Кто провёл наибольшее количество матчей за Зенит (456 игр)?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Провёл за команду 456 матчей (в период с 1975 по 1988 и 1997 годы)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Анатолий Давыдов</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Вячеслав Малафеев</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Лев Бурчалкин</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Александр Анюков</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Александр Кержаков</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Павел Садырин</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Как зовут главного тренера Зенита?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>zs_semak</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Главный тренер с 2018 года. Является игроком Зенита в прошлом. Провёл за клуб 48 матчей и забил 9 голов</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>zs_semak</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Сергей Семак</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Андрей Талалаев</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Вадим Евсеев</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Владимир Федотов</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Владимир Вайсс</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Андрей Тихонов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dinamo_fomin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>28-летний (02.03.1997) российский опорник</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dinamo_fomin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Даниил Фомин</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Данил Глебов</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Егор Смелов</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Ульви Бабаев</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Александр Куцицкий</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Андрей Кудравец</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dinamo_sergeev</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>30-летний (11.05.1995) российский нападающий</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dinamo_sergeev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Иван Сергеев</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Константин Тюкавин</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ярослав Гладышев</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Андрей Лунёв</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Максим Осипенко</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Данил Глебов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dinamo_rikardo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>23-летний (21.12.2002) бразильский защитник</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dinamo_rikardo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Дэвид Рикардо</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Роберто Фернандес</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Николас Маричаль</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Диего Лаксальт</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Хуан Хосе Касерес</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Рубенс Диас</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Кто этот футболист?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dinamo_osipenko</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>31-летний (16.05.1994) российский центральный защитник</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dinamo_osipenko</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Максим Осипенко</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Андрей Лунёв</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Александр Куцицкий</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Ульви Бабаев</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Иван Сергеев</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Ярослав Гладышев</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Кто из этих футболистов никогда не играл за Динамо Москва?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Федор Черенков никогда не выступал за Динамо</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Федор Черенков</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Денис Колодин</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ролан Гусев</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Дмитрий Булыкин</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Александр Кержаков</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Дмитрий Черышев</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>В каком из этих сезонов Динамо Москва выиграло Кубок России?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Динамо выиграло свой единственный Кубок России в сезоне 1995</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1994/1995</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1996/1997</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1999/2000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2002/2003</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1992/1993</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2009/2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>В каком году Динамо М выиграло свой последний на данный момент трофей?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Свой последний трофей завоевал в 1995 году — Кубок России.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1995 год</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1992 год</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2000 год</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2010 год</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2005 год</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1997 год</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Как зовут главного тренера Динамо Москва?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dinamo_shzwarz</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Главный тренер</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>dinamo_shzwarz</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Сандро Шварц</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Марко Николич</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Владимир Ивич</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Валерий Карпин</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Марцел Личка</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Дан Петреску</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>С какой командой играл Зенит в прошлом туре?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Зенит 1:2 Родина</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Родина</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>logo_ks</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Крылья Советов</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>logo_orenburg</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Оренбург</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>logo_lokomotiv</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Локомотив</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>logo_rostov</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>С кем сыграет Зенит в следующем туре?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5 тур. 23.08, 22:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Динамо Москва</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>logo_akron</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Акрон</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Родина</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>С какой командой играл Динамо Москва в прошлом туре?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Динамо Москва 3:1 Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>logo_rostov</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>logo_akron</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Акрон</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>С кем сыграет Динамо Москва в следующем туре?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5 тур. 23.08, 17:15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>logo_rodina</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Родина</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>logo_rubin</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Рубин</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>logo_lokomotiv</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Локомотив</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Кто лидирует в РПЛ после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>logo_rpl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9 очков</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>logo_akhmat</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ахмат</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>logo_cska</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ЦСКА</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>На каком месте находится Зенит после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6 очков</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2 место</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5 место</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>4 место</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3 место</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6 место</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1 место</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>На каком месте находится Динамо Москва после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4 очков</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8 место</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10 место</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>6 место</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5 место</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>9 место</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>11 место</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Кто является лучшим бомбардиром РПЛ после 3 туров?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>logo_rpl</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Забил 4 голов в 3 матчах</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Максим Глушенков</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Никита Кривцов</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Мирлинд Даку</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Александр Соболев</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Алексей Сутормин</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Даниил Шанталий</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Какая из команд набрала больше очков в последних 5 матчах?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>logo_rpl</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Зенит: 12 очков, Динамо Москва: 10 очков</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>logo_dinamo</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Динамо Москва</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>logo_rubin</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Рубин</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>logo_dinamo_mah</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Кто чаще побеждал в очных противостояниях, Зенит или Динамо Москва?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_zenit_dinmos_quest.jpg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Официальные: победы Зенит — 59, Динамо Москва — 70</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_zenit_dinmos_quest.jpg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Динамо Москва</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Поровну</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Ничья</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Никто</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Затрудняюсь ответить</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>С каким счетом завершилась их последняя встреча?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_zenit_dinmos_quest.jpg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_zenit_dinmos_quest.jpg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 1:3 Зенит</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 2:3 Зенит</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 1:4 Зенит</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 0:3 Зенит</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 1:2 Зенит</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Динамо Москва 3:1 Зенит</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>textQue</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>slugQue</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>slugDlg</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>slugCorAns</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>txtCorAns</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>wrSlgAns1</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>wrTxtAns1</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>wrSlgAns2</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>wrTxtAns2</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>wrSlgAns3</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>wrTxtAns3</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>wrSlgAns4</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>wrTxtAns4</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>wrSlgAns5</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>wrTxtAns5</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>position</t>
         </is>
       </c>
     </row>
@@ -918,13 +5584,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>spartak_djiku</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>cska_alves</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21-летний (05.03.2005) бразильский полузащитник</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>spartak_djiku</t>
+          <t>cska_alves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -934,7 +5604,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Александер Джику</t>
+          <t>Матеуш Алвес</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -944,7 +5614,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Манфред Угальде</t>
+          <t>Виллиан Роша</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -954,7 +5624,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Кристофер Мартинс</t>
+          <t>Кельвен</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -964,7 +5634,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Эсекьель Барко</t>
+          <t>Алеррандро</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -974,7 +5644,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Пабло Солари</t>
+          <t>Адольфо Гайч</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -984,7 +5654,20 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Тео Бонгонда</t>
+          <t>Энрике Кармо</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>21</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Бразилия</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Полузащитник</t>
         </is>
       </c>
     </row>
@@ -999,13 +5682,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spartak_parada</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>cska_krugovoy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>28-летний (28.05.1998) российский левый защитник. Воспитанник «Зенита», но летом 2024 был куплен ЦСКА за ~€2 млн</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>spartak_parada</t>
+          <t>cska_krugovoy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1015,7 +5702,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Виктор Парада</t>
+          <t>Данил Круговой</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1025,7 +5712,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Рикардо Мангас</t>
+          <t>Игорь Акинфеев</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1035,7 +5722,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Кристофер Мартинс</t>
+          <t>Владислав Тороп</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1045,7 +5732,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Эсекьель Барко</t>
+          <t>Игорь Дивеев</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1055,7 +5742,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Тео Бонгонда</t>
+          <t>Андрей Савинов</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1065,7 +5752,20 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Хесус Медина</t>
+          <t>Артем Шуманский</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Защитник</t>
         </is>
       </c>
     </row>
@@ -1080,17 +5780,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spartak_barco</t>
+          <t>cska_borisko</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27-летний (29.03.1999) аргентинский атакующий полузащитник. Перешёл 25 июля 2024 из «Ривер Плейт» за ≈ €8 млн</t>
+          <t>26-летний (15.02.2000) российский вратарь</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>spartak_barco</t>
+          <t>cska_borisko</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1100,7 +5800,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Эсекьель Барко</t>
+          <t>Максим Бориско</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1110,7 +5810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Рикардо Мангас</t>
+          <t>Имран Фиров</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1120,7 +5820,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Кристофер Мартинс</t>
+          <t>Кирилл Глебов</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1130,7 +5830,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Пабло Солари</t>
+          <t>Иван Обляков</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1140,7 +5840,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Манфред Угальде</t>
+          <t>Даниил Круговой</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1150,7 +5850,20 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Хесус Медина</t>
+          <t>Данила Козлов</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>26</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Вратарь</t>
         </is>
       </c>
     </row>
@@ -1165,13 +5878,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spartak_daku</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>cska_kislyak</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20-летний (09.01.2006) российский атакующий полузащитник. Дебютировал за основную команду весной 2025 после яркой игры в ЮФЛ</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>spartak_daku</t>
+          <t>cska_kislyak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1181,7 +5898,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Мирлинд Даку</t>
+          <t>Матвей Кисляк</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1191,7 +5908,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Кристофер Ву</t>
+          <t>Игорь Дивеев</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1201,7 +5918,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Кристофер Мартинс</t>
+          <t>Максим Мухин</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1211,7 +5928,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Жедсон Фернандеш</t>
+          <t>Андрей Савинов</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1221,7 +5938,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Пабло Солари</t>
+          <t>Егор Ушаков</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1231,7 +5948,20 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Срджан Бабич</t>
+          <t>Матвей Лукин</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Полузащитник</t>
         </is>
       </c>
     </row>
@@ -1241,22 +5971,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Какого футболиста Спартака дисквалифицировали из-за содержании в крови бромантана?</t>
+          <t>Под каким номером играет легенда ЦСКА - Игорь Акинфеев?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>cska_akinfeev</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2003 год</t>
+          <t>Вратарь</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>spartak_titov</t>
+          <t>cska_akinfeev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1266,7 +5996,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Егор Титов</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1276,7 +6006,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Илья Цымбаларь</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1286,7 +6016,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Андрей Тихонов</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1296,7 +6026,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Вадим Евсеев</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1306,7 +6036,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Александр Филимонов</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1316,17 +6046,20 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Дмитрий Хлестов</t>
-        </is>
-      </c>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Какой бывший главный тренер Спартака вывел Швейцарию в 1/4 на ЧМ-2026?</t>
+          <t>Сколько раз ЦСКА выигрывал Суперкубок России?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1336,12 +6069,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2014—2015 года</t>
+          <t>2001/02,  2004/05,  2005/06,  2007/08,  2008/09,  2010/11,  2012/13,  2022/23, 2024/25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1351,7 +6084,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Мурат Якин</t>
+          <t>Восемь</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1361,7 +6094,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Унаи Эмери</t>
+          <t>Шесть</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1371,7 +6104,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Руй Витория</t>
+          <t>Пять</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1381,7 +6114,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Массимо Каррера </t>
+          <t>Четыре</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1391,7 +6124,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Невио Скала</t>
+          <t>Девять</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1401,9 +6134,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рауль Рианчо </t>
-        </is>
-      </c>
+          <t>Семь</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,7 +6147,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Каким было последнее название Спартака до 1934 года?</t>
+          <t>Какой европейский клубный турнир выиграл ЦСКА в сезоне 2004/05?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,10 +6155,14 @@
           <t>no_pic</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>В сезоне 2004/05 ЦСКА стал обладателем Кубка УЕФА.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1432,7 +6172,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Промкооперация</t>
+          <t>Кубок УЕФА</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1442,7 +6182,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Пищевики</t>
+          <t>Лигу чемпионов УЕФА</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1452,7 +6192,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Дукат</t>
+          <t>Кубок обладателей кубков</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1462,7 +6202,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Красная Пресня</t>
+          <t>Кубок Интертото</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1472,7 +6212,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>РГО Сокол</t>
+          <t>Суперкубок УЕФА</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1482,9 +6222,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Московский клуб спорта</t>
-        </is>
-      </c>
+          <t>Лигу конференций УЕФА</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,22 +6235,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Как зовут главного тренера Спартака?</t>
+          <t>Как зовут главного тренера ЦСКА?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spartak_carsedo</t>
+          <t>cska_igdisamov</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Главный тренер</t>
+          <t>Возглавил ЦСКА летом 2026 года. Ранее, 4 мая 2026 года, был назначен исполняющим обязанности главного тренера основной команды</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>spartak_carsedo</t>
+          <t>cska_igdisamov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1517,7 +6260,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Хуан Карседо</t>
+          <t>Дмитрий Игдисамов</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1527,7 +6270,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Владимир Слишкович</t>
+          <t>Марко Николич</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1537,7 +6280,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Доменико Тедеско</t>
+          <t>Славолюб Муслин</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1547,7 +6290,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Димитр Димитров</t>
+          <t>Владимир Ивич</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1557,7 +6300,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Владимир Вайсс</t>
+          <t>Саша Илич</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,9 +6310,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Миодраг Божович</t>
-        </is>
-      </c>
+          <t>Фабио Челестини</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,17 +6328,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>krasnodar_costa</t>
+          <t>lokomotiv_pinyaev</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27-летний (21.07.1999) бразильский центральный защитник</t>
+          <t>21-летний (02.11.2004) российский левый вингер</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>krasnodar_costa</t>
+          <t>lokomotiv_pinyaev</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1602,7 +6348,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Диего Коста</t>
+          <t>Сергей Пиняев</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1612,7 +6358,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Витор Тормена</t>
+          <t>Дмитрий Баринов</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1622,7 +6368,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Джубал</t>
+          <t>Максим Ненахов</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1632,7 +6378,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Джованни Гонсалес</t>
+          <t>Алексей Батраков</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1642,7 +6388,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Лукас Олаза</t>
+          <t>Артем Тимофеев</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,7 +6398,20 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Кевин Ленини</t>
+          <t>Александр Сильянов</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>21</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Полузащитник</t>
         </is>
       </c>
     </row>
@@ -1667,17 +6426,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>krasnodar_batxi</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>28-летний (01.05.1998) ангольский полузащитник</t>
-        </is>
-      </c>
+          <t>lokomotiv_dzhikiya</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>krasnodar_batxi</t>
+          <t>lokomotiv_dzhikiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1687,7 +6442,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Батчи</t>
+          <t>Георгий Джикия</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1697,7 +6452,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Диего Коста</t>
+          <t>Зелимхан Бакаев</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1707,7 +6462,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Витор Тормена</t>
+          <t>Илья Лантратов</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1717,7 +6472,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Джубал</t>
+          <t>Даниил Веселов</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1727,7 +6482,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Лукас Олаза</t>
+          <t>Александр Сильянов</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1737,7 +6492,20 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Джованни Гонсалес</t>
+          <t>Егор Погостнов</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>32</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Защитник</t>
         </is>
       </c>
     </row>
@@ -1752,17 +6520,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>krasnodar_lenini</t>
+          <t>lokomotiv_fasson</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29-летний (27.01.1997) кабо-вердианский опорный полузащитник</t>
+          <t>25-летний (30.05.2001) бразильский центрбек</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>krasnodar_lenini</t>
+          <t>lokomotiv_fasson</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1772,7 +6540,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Кевин Ленини</t>
+          <t>Лукас Фассон</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1782,7 +6550,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Диего Коста</t>
+          <t>Жерзино Ньямси</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1792,7 +6560,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Витор Тормена</t>
+          <t>Сесар Монтес</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1802,7 +6570,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Джубал</t>
+          <t>Марк Мампасси</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1812,7 +6580,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Лукас Олаза</t>
+          <t>Артем Карпукас</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1822,7 +6590,20 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Джованни Гонсалес</t>
+          <t>Николай Комличенко</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>25</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Бразилия</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Защитник</t>
         </is>
       </c>
     </row>
@@ -1837,17 +6618,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>krasnodar_petrov</t>
+          <t>lokomotiv_nenakhov</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35-летний (02.01.1991) российский правый защитник. В клубе с января 2013</t>
+          <t>27-летний (13.12.1998) российский правый защитник</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>krasnodar_petrov</t>
+          <t>lokomotiv_nenakhov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1857,7 +6638,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Сергей Петров</t>
+          <t>Максим Ненахов</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1867,7 +6648,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Станислав Агкатцев</t>
+          <t>Дмитрий Баринов</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1877,7 +6658,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Александр Корякин</t>
+          <t>Алексей Батраков</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1887,7 +6668,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Даниил Голиков</t>
+          <t>Артем Тимофеев</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1897,7 +6678,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Роман Сафронов</t>
+          <t>Александр Сильянов</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1907,7 +6688,20 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Дмитрий Кучугура</t>
+          <t>Константин Марадишвили</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>27</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Защитник</t>
         </is>
       </c>
     </row>
@@ -1917,7 +6711,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Какой тренер вывел Краснодар в РПЛ впервые в истории?</t>
+          <t>В каком году был основан Локомотив?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1927,12 +6721,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>В 2010 году ФК Сатурн подал заявление о выходе из премьер-лиги и на его место был взят, занявщий 5-е место ФК Краснодар. Сергей Ташуев к тому времени уже не работал.</t>
+          <t>Локомотив Москва был основан в 1922 году</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1942,7 +6736,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Сергей Ташуев</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1952,7 +6746,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Павел Садырин</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1962,7 +6756,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Виктор Гончаренко</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1972,7 +6766,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Мурад Мусаев</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1982,7 +6776,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Александр Кузнецов</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1992,9 +6786,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Олег Кононов</t>
-        </is>
-      </c>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2002,7 +6799,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Какое животное является талисманом Краснодара?</t>
+          <t>В каком сезоне Локомотив в последний раз становился чемпионом?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2012,12 +6809,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Талисманом Краснодара является бык, который также размещён на эмблеме клуба</t>
+          <t>5 мая 2018 года после домашней победы над «Зенитом» в матче 29-го тура Локомотив в третий раз стал чемпионом России</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mas_krasnodar</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2027,7 +6824,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Бык</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2037,7 +6834,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Конь</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2047,7 +6844,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Лев</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2057,7 +6854,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Журавль</t>
+          <t>2014/15</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2067,7 +6864,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Дракон</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2077,9 +6874,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Волк</t>
-        </is>
-      </c>
+          <t>2019/20</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2087,7 +6887,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Кто является рекордсменом Краснодара по количеству проведенных игр во всех турнирах?</t>
+          <t>Кто провел больше всех матчей за Локомотив среди легионеров?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2097,12 +6897,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>На счету Сергея Петрова 304 матча в футболке Краснодара</t>
+          <t>334 матча</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>krasnodar_petrov</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2112,7 +6912,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Сергей Петров</t>
+          <t>Сергей Гуренко</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2122,7 +6922,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Матвей Сафонов</t>
+          <t>Ведран Чорлука</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2132,7 +6932,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Александр Мартынович</t>
+          <t>Заза Джанашия</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2142,7 +6942,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Жоаозиньо</t>
+          <t>Майкон</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2152,7 +6952,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Юрий Газинский</t>
+          <t>Ян Дюрица</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2162,9 +6962,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Маурисио Перейра</t>
-        </is>
-      </c>
+          <t>Мануэл Фернандеш</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2172,12 +6975,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Как зовут главного тренера Краснодара?</t>
+          <t>Как зовут главного тренера Локомотива?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>krasnodar_musaev</t>
+          <t>lokomotiv_galaktionov</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2187,7 +6990,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>krasnodar_musaev</t>
+          <t>lokomotiv_galaktionov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2197,7 +7000,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Мурад Мусаев</t>
+          <t>Михаил Галактионов</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2207,7 +7010,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Рашид Рахимов</t>
+          <t>Вячеслав Мельников</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2217,7 +7020,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Магомед Адиев</t>
+          <t>Александр Цыганков</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2227,7 +7030,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Игорь Осинькин</t>
+          <t>Александр Точилин</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2237,7 +7040,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Александр Тарханов</t>
+          <t>Роберт Евдокимов</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2247,9 +7050,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Юрий Нагайцев</t>
-        </is>
-      </c>
+          <t>Мирослав Ромащенко</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2257,84 +7063,87 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>С какой командой играл Спартак в прошлом туре?</t>
+          <t>С какой командой играл ЦСКА в прошлом туре?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>logo_cska</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 1:0 Факел</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>logo_fakel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Факел</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>logo_baltika</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>logo_rubin</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Рубин</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>logo_orenburg</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Оренбург</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>logo_spartak</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ахмат 1:2 Спартак Москва</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>logo_akhmat</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>logo_akhmat</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Ахмат</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>logo_zenit</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Зенит</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>logo_fakel</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Факел</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>logo_rubin</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Рубин</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>logo_dinamo</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Динамо Москва</t>
+          <t>Спартак</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>logo_baltika</t>
+          <t>logo_dinamo_mah</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Балтика</t>
-        </is>
-      </c>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2342,52 +7151,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>С кем сыграет Спартак в следующем туре?</t>
+          <t>С кем сыграет ЦСКА в следующем туре?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>logo_cska</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4 тур. 16.08, 21:30</t>
+          <t>6 тур. 28.08, 19:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>logo_baltika</t>
+          <t>logo_akron</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>logo_baltika</t>
+          <t>logo_akron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Балтика</t>
+          <t>Акрон</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>logo_lokomotiv</t>
+          <t>logo_ks</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Локомотив</t>
+          <t>Крылья Советов</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>logo_ks</t>
+          <t>logo_fakel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Крылья Советов</t>
+          <t>Факел</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2402,24 +7211,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>logo_dinamo_mah</t>
+          <t>logo_zenit</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Динамо Махачкала</t>
+          <t>Зенит</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>logo_akron</t>
+          <t>logo_rostov</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Акрон</t>
-        </is>
-      </c>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2427,84 +7239,87 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>С какой командой играл Краснодар в прошлом туре?</t>
+          <t>С какой командой играл Локомотив в прошлом туре?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>logo_lokomotiv</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Оренбург 1:1 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>logo_orenburg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>logo_orenburg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Оренбург</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>logo_krasnodar</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Краснодар 3:2 Факел</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>logo_fakel</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>logo_fakel</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Факел</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>logo_spartak</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Спартак</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>logo_zenit</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Зенит</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>logo_rodina</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Родина</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>logo_zenit</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Зенит</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>logo_lokomotiv</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Локомотив</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>logo_dinamo_mah</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Динамо Махачкала</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>logo_akhmat</t>
+          <t>logo_baltika</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Ахмат</t>
-        </is>
-      </c>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2512,42 +7327,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>С кем сыграет Краснодар в следующем туре?</t>
+          <t>С кем сыграет Локомотив в следующем туре?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4 тур. 15.08, 22:45</t>
+          <t>6 тур. 29.08, 21:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>logo_akhmat</t>
+          <t>logo_dinamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>logo_akhmat</t>
+          <t>logo_dinamo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ахмат</t>
+          <t>Динамо Москва</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>logo_akron</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Спартак</t>
+          <t>Акрон</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2562,34 +7377,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>logo_orenburg</t>
+          <t>logo_ks</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Крылья Советов</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>logo_rostov</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>logo_cska</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ЦСКА</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>logo_ks</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Крылья Советов</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2597,7 +7415,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Кто лидирует в РПЛ после 3 туров?</t>
+          <t>Кто лидирует в РПЛ после 4 туров?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2607,32 +7425,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6 очков</t>
+          <t>12 очков</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>logo_zenit</t>
+          <t>logo_krasnodar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>logo_zenit</t>
+          <t>logo_krasnodar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Зенит</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>logo_rodina</t>
+          <t>logo_orenburg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Родина</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2647,34 +7465,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>logo_akhmat</t>
+          <t>logo_rostov</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Ахмат</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>logo_baltika</t>
+          <t>logo_rubin</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Балтика</t>
+          <t>Рубин</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>logo_rostov</t>
+          <t>logo_dinamo</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Ростов</t>
-        </is>
-      </c>
+          <t>Динамо Москва</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2682,84 +7503,87 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>На каком месте находится Спартак после 3 туров?</t>
+          <t>На каком месте находится ЦСКА после 4 туров?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>logo_cska</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6 очков</t>
+          <t>8 очков</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>logo_cska</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>num_5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5 место</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>num_8</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8 место</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>num_6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6 место</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>num_9</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9 место</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>num_7</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>7 место</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>num_2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>2 место</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>num_3</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3 место</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>num_6</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>6 место</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>num_4</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>4 место</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>num_5</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>5 место</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>num_1</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1 место</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2767,84 +7591,87 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>На каком месте находится Краснодар после 3 туров?</t>
+          <t>На каком месте находится Локомотив после 4 туров?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6 очков</t>
+          <t>3 очков</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>num_3</t>
+          <t>num_12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3 место</t>
+          <t>12 место</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>num_6</t>
+          <t>num_11</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6 место</t>
+          <t>11 место</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>num_2</t>
+          <t>num_10</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2 место</t>
+          <t>10 место</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>num_1</t>
+          <t>num_14</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1 место</t>
+          <t>14 место</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>num_7</t>
+          <t>num_13</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>7 место</t>
+          <t>13 место</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>num_5</t>
+          <t>num_16</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5 место</t>
-        </is>
-      </c>
+          <t>16 место</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2852,7 +7679,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Какая из команд набрала больше очков в последних 5 матчах?</t>
+          <t>Кто является лучшим бомбардиром РПЛ после 4 туров?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2862,159 +7689,165 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Спартак: 9 очков, Краснодар: 11 очков</t>
+          <t>Забил 5 голов в 4 матчах</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>logo_krasnodar</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Максим Глушенков</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>logo_spartak</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Спартак</t>
+          <t>Александр Соболев</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>logo_dinamo_mah</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Динамо Махачкала</t>
+          <t>Артём Максименко</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>logo_akron</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Акрон</t>
+          <t>Никита Кривцов</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>logo_ks</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Крылья Советов</t>
+          <t>Мирлинд Даку</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>logo_rubin</t>
+          <t>no_pic</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Рубин</t>
-        </is>
-      </c>
+          <t>Брайан Хиль</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Кто чаще побеждал в очных противостояниях, Спартак или Краснодар?</t>
+          <t>Какая из команд набрала больше очков в последних 5 матчах?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+          <t>logo_rpl</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Официальные: победы Спартак — 22, Краснодар — 13</t>
+          <t>ЦСКА: 8 очков, Локомотив: 2 очков</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
+          <t>logo_cska</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>logo_cska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Спартак</t>
+          <t>ЦСКА</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>logo_lokomotiv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Локомотив</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>logo_krasnodar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Поровну</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>logo_fakel</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ничья</t>
+          <t>Факел</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>logo_akhmat</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Никто</t>
+          <t>Ахмат</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>no_pic</t>
+          <t>logo_dinamo_mah</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Затрудняюсь ответить</t>
-        </is>
-      </c>
+          <t>Динамо Махачкала</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3022,80 +7855,171 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Кто чаще побеждал в очных матчах?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>two_teams</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Официальные матчи: ЦСКА – 81 побед, Локомотив – 57 побед</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>two_teams</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 81, Локомотив – 57</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 82, Локомотив – 57</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 81, Локомотив – 58</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 80, Локомотив – 57</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 81, Локомотив – 56</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ЦСКА – 57, Локомотив – 81</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>С каким счетом завершилась их последняя встреча?</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 1:2 Краснодар</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 2:2 Краснодар</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 1:3 Краснодар</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 0:2 Краснодар</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 1:1 Краснодар</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>no_pic</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Спартак Москва 2:1 Краснодар</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>two_teams</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>two_teams</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 3:1 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 4:1 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 3:2 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 2:1 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 3:0 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>no_pic</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ЦСКА Москва 1:3 Локомотив Москва</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content/src-assets/data/Матч Тура/Матч Тура 26-27.xlsx
+++ b/content/src-assets/data/Матч Тура/Матч Тура 26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SvyTo\Documents\GitHub\footballquiz\src\assets\data\Матч Тура\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65C5248-D0C3-4666-81E7-6B776A366296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A927B2B-5E86-4187-8223-63733D679BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="-180" windowWidth="29160" windowHeight="15960" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-180" yWindow="-180" windowWidth="29160" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mt_cska_baltika" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="563">
   <si>
     <t>type</t>
   </si>
@@ -562,9 +562,6 @@
     <t>Ростов</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>На каком месте находится Спартак после 3 туров?</t>
   </si>
   <si>
@@ -604,9 +601,6 @@
     <t>Кто чаще побеждал в очных противостояниях, Спартак или Краснодар?</t>
   </si>
   <si>
-    <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_spartak_krasnodar_quest.jpg</t>
-  </si>
-  <si>
     <t>Официальные: победы Спартак — 22, Краснодар — 13</t>
   </si>
   <si>
@@ -1028,9 +1022,6 @@
   </si>
   <si>
     <t>Кто чаще побеждал в очных противостояниях, Зенит или Динамо Москва?</t>
-  </si>
-  <si>
-    <t>https://amaranth64.github.io/RPL_V2/matchday/images/mt_zenit_dinmos_quest.jpg</t>
   </si>
   <si>
     <t>Официальные: победы Зенит — 59, Динамо Москва — 70</t>
@@ -3432,11 +3423,11 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
         <v>177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>178</v>
       </c>
       <c r="C23" t="s">
         <v>60</v>
@@ -3451,45 +3442,45 @@
         <v>24</v>
       </c>
       <c r="G23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
         <v>179</v>
       </c>
-      <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
         <v>180</v>
       </c>
-      <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
         <v>181</v>
       </c>
-      <c r="L23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" t="s">
         <v>182</v>
       </c>
-      <c r="N23" t="s">
-        <v>24</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="s">
         <v>183</v>
       </c>
-      <c r="P23" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" t="s">
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B24" t="s">
-        <v>185</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
@@ -3504,37 +3495,37 @@
         <v>24</v>
       </c>
       <c r="G24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
         <v>180</v>
       </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" t="s">
-        <v>181</v>
-      </c>
       <c r="J24" t="s">
         <v>24</v>
       </c>
       <c r="K24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L24" t="s">
         <v>24</v>
       </c>
       <c r="M24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s">
         <v>24</v>
       </c>
       <c r="O24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s">
         <v>24</v>
       </c>
       <c r="Q24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3542,13 +3533,13 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C25" t="s">
         <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E25" t="s">
         <v>106</v>
@@ -3557,7 +3548,7 @@
         <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
         <v>60</v>
@@ -3595,16 +3586,16 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
         <v>190</v>
       </c>
-      <c r="C26" t="s">
-        <v>191</v>
-      </c>
-      <c r="D26" t="s">
-        <v>192</v>
-      </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -3616,31 +3607,31 @@
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J26" t="s">
         <v>24</v>
       </c>
       <c r="K26" t="s">
+        <v>191</v>
+      </c>
+      <c r="L26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" t="s">
+        <v>192</v>
+      </c>
+      <c r="N26" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" t="s">
         <v>193</v>
       </c>
-      <c r="L26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="P26" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" t="s">
         <v>194</v>
-      </c>
-      <c r="N26" t="s">
-        <v>24</v>
-      </c>
-      <c r="O26" t="s">
-        <v>195</v>
-      </c>
-      <c r="P26" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -3648,49 +3639,49 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
         <v>197</v>
       </c>
-      <c r="C27" t="s">
-        <v>191</v>
-      </c>
-      <c r="E27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="s">
         <v>198</v>
       </c>
-      <c r="H27" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
         <v>199</v>
       </c>
-      <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="N27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" t="s">
         <v>200</v>
       </c>
-      <c r="L27" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="P27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
         <v>201</v>
-      </c>
-      <c r="N27" t="s">
-        <v>24</v>
-      </c>
-      <c r="O27" t="s">
-        <v>202</v>
-      </c>
-      <c r="P27" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3764,49 +3755,49 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
         <v>205</v>
       </c>
-      <c r="E2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
         <v>206</v>
       </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
         <v>207</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
         <v>208</v>
       </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
         <v>209</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>210</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -3817,49 +3808,49 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
         <v>212</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
         <v>213</v>
       </c>
-      <c r="E3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
         <v>214</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>216</v>
-      </c>
       <c r="N3" t="s">
         <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P3" t="s">
         <v>24</v>
       </c>
       <c r="Q3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -3870,49 +3861,49 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>217</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
         <v>218</v>
       </c>
-      <c r="E4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
         <v>219</v>
       </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
         <v>220</v>
       </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="s">
         <v>221</v>
       </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
         <v>222</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" t="s">
-        <v>223</v>
-      </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -3923,49 +3914,49 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>213</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
         <v>214</v>
       </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>216</v>
-      </c>
       <c r="N5" t="s">
         <v>24</v>
       </c>
       <c r="O5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P5" t="s">
         <v>24</v>
       </c>
       <c r="Q5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -3973,13 +3964,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
         <v>141</v>
@@ -3988,37 +3979,37 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>228</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
         <v>229</v>
       </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
         <v>230</v>
       </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
         <v>231</v>
       </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
         <v>232</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" t="s">
-        <v>233</v>
-      </c>
-      <c r="P6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -4026,7 +4017,7 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
@@ -4038,13 +4029,13 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J7" t="s">
         <v>24</v>
@@ -4056,19 +4047,19 @@
         <v>24</v>
       </c>
       <c r="M7" t="s">
+        <v>236</v>
+      </c>
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
+        <v>237</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
         <v>238</v>
-      </c>
-      <c r="N7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" t="s">
-        <v>239</v>
-      </c>
-      <c r="P7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -4076,13 +4067,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
         <v>141</v>
@@ -4091,31 +4082,31 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>242</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
         <v>243</v>
       </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
         <v>244</v>
       </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
         <v>245</v>
-      </c>
-      <c r="L8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" t="s">
-        <v>246</v>
-      </c>
-      <c r="N8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" t="s">
-        <v>247</v>
       </c>
       <c r="P8" t="s">
         <v>24</v>
@@ -4129,28 +4120,28 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" t="s">
         <v>248</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
         <v>249</v>
       </c>
-      <c r="D9" t="s">
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
         <v>250</v>
-      </c>
-      <c r="E9" t="s">
-        <v>249</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>251</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
-        <v>252</v>
       </c>
       <c r="J9" t="s">
         <v>24</v>
@@ -4162,7 +4153,7 @@
         <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N9" t="s">
         <v>24</v>
@@ -4185,49 +4176,49 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
         <v>254</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
         <v>255</v>
       </c>
-      <c r="E10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
         <v>256</v>
       </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" t="s">
         <v>257</v>
       </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" t="s">
         <v>258</v>
       </c>
-      <c r="L10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
         <v>259</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" t="s">
-        <v>260</v>
-      </c>
-      <c r="P10" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -4238,49 +4229,49 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
         <v>262</v>
       </c>
-      <c r="D11" t="s">
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
         <v>263</v>
       </c>
-      <c r="E11" t="s">
-        <v>262</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
         <v>264</v>
       </c>
-      <c r="H11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
         <v>265</v>
       </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" t="s">
         <v>266</v>
       </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>267</v>
-      </c>
-      <c r="N11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" t="s">
-        <v>268</v>
-      </c>
       <c r="P11" t="s">
         <v>24</v>
       </c>
       <c r="Q11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -4291,49 +4282,49 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
         <v>269</v>
       </c>
-      <c r="D12" t="s">
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
         <v>270</v>
       </c>
-      <c r="E12" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
         <v>271</v>
       </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
         <v>272</v>
       </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" t="s">
         <v>273</v>
       </c>
-      <c r="L12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" t="s">
         <v>274</v>
-      </c>
-      <c r="N12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O12" t="s">
-        <v>275</v>
-      </c>
-      <c r="P12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -4344,49 +4335,49 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J13" t="s">
         <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L13" t="s">
         <v>24</v>
       </c>
       <c r="M13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N13" t="s">
         <v>24</v>
       </c>
       <c r="O13" t="s">
+        <v>262</v>
+      </c>
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="s">
         <v>264</v>
-      </c>
-      <c r="P13" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -4394,13 +4385,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E14" t="s">
         <v>147</v>
@@ -4409,37 +4400,37 @@
         <v>24</v>
       </c>
       <c r="G14" t="s">
+        <v>279</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
         <v>281</v>
       </c>
-      <c r="H14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
         <v>282</v>
       </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="N14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
+        <v>245</v>
+      </c>
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="s">
         <v>283</v>
-      </c>
-      <c r="L14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" t="s">
-        <v>284</v>
-      </c>
-      <c r="N14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" t="s">
-        <v>247</v>
-      </c>
-      <c r="P14" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -4447,13 +4438,13 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E15" t="s">
         <v>147</v>
@@ -4462,37 +4453,37 @@
         <v>24</v>
       </c>
       <c r="G15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>287</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
         <v>288</v>
       </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
         <v>289</v>
       </c>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" t="s">
         <v>290</v>
       </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="s">
         <v>291</v>
-      </c>
-      <c r="N15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O15" t="s">
-        <v>292</v>
-      </c>
-      <c r="P15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -4500,13 +4491,13 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E16" t="s">
         <v>147</v>
@@ -4515,37 +4506,37 @@
         <v>24</v>
       </c>
       <c r="G16" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
         <v>296</v>
       </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
         <v>297</v>
       </c>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
         <v>298</v>
       </c>
-      <c r="L16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="P16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="s">
         <v>299</v>
-      </c>
-      <c r="N16" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" t="s">
-        <v>300</v>
-      </c>
-      <c r="P16" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -4553,52 +4544,52 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D17" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
+        <v>301</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>302</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
         <v>303</v>
       </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
         <v>304</v>
       </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
         <v>305</v>
       </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
         <v>306</v>
       </c>
-      <c r="L17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="P17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="s">
         <v>307</v>
-      </c>
-      <c r="N17" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" t="s">
-        <v>308</v>
-      </c>
-      <c r="P17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -4606,13 +4597,13 @@
         <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C18" t="s">
         <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E18" t="s">
         <v>163</v>
@@ -4659,13 +4650,13 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C19" t="s">
         <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E19" t="s">
         <v>60</v>
@@ -4692,7 +4683,7 @@
         <v>106</v>
       </c>
       <c r="M19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N19" t="s">
         <v>159</v>
@@ -4712,13 +4703,13 @@
         <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C20" t="s">
         <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E20" t="s">
         <v>157</v>
@@ -4765,13 +4756,13 @@
         <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
         <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E21" t="s">
         <v>163</v>
@@ -4824,7 +4815,7 @@
         <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E22" t="s">
         <v>106</v>
@@ -4833,7 +4824,7 @@
         <v>106</v>
       </c>
       <c r="G22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
         <v>139</v>
@@ -4871,7 +4862,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C23" t="s">
         <v>141</v>
@@ -4886,37 +4877,37 @@
         <v>24</v>
       </c>
       <c r="G23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>182</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
         <v>179</v>
       </c>
-      <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="N23" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" t="s">
+        <v>180</v>
+      </c>
+      <c r="P23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="s">
         <v>183</v>
-      </c>
-      <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" t="s">
-        <v>182</v>
-      </c>
-      <c r="L23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" t="s">
-        <v>180</v>
-      </c>
-      <c r="N23" t="s">
-        <v>24</v>
-      </c>
-      <c r="O23" t="s">
-        <v>181</v>
-      </c>
-      <c r="P23" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -4924,13 +4915,13 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
         <v>147</v>
       </c>
       <c r="D24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E24" t="s">
         <v>147</v>
@@ -4939,37 +4930,37 @@
         <v>24</v>
       </c>
       <c r="G24" t="s">
+        <v>320</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
+        <v>321</v>
+      </c>
+      <c r="J24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" t="s">
+        <v>180</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
+        <v>182</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" t="s">
         <v>322</v>
       </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="P24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" t="s">
         <v>323</v>
-      </c>
-      <c r="J24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" t="s">
-        <v>181</v>
-      </c>
-      <c r="L24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" t="s">
-        <v>183</v>
-      </c>
-      <c r="N24" t="s">
-        <v>24</v>
-      </c>
-      <c r="O24" t="s">
-        <v>324</v>
-      </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -4977,13 +4968,13 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C25" t="s">
         <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -4992,13 +4983,13 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J25" t="s">
         <v>24</v>
@@ -5010,19 +5001,19 @@
         <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N25" t="s">
         <v>24</v>
       </c>
       <c r="O25" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P25" t="s">
         <v>24</v>
       </c>
       <c r="Q25" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -5030,13 +5021,13 @@
         <v>136</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
         <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E26" t="s">
         <v>141</v>
@@ -5083,16 +5074,16 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C27" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E27" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -5110,25 +5101,25 @@
         <v>24</v>
       </c>
       <c r="K27" t="s">
+        <v>191</v>
+      </c>
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
+        <v>192</v>
+      </c>
+      <c r="N27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" t="s">
         <v>193</v>
       </c>
-      <c r="L27" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="P27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
         <v>194</v>
-      </c>
-      <c r="N27" t="s">
-        <v>24</v>
-      </c>
-      <c r="O27" t="s">
-        <v>195</v>
-      </c>
-      <c r="P27" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -5136,49 +5127,49 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>332</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
         <v>333</v>
       </c>
-      <c r="E28" t="s">
-        <v>333</v>
-      </c>
-      <c r="F28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" t="s">
+        <v>334</v>
+      </c>
+      <c r="L28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" t="s">
         <v>335</v>
       </c>
-      <c r="H28" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="N28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O28" t="s">
         <v>336</v>
       </c>
-      <c r="J28" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="P28" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="s">
         <v>337</v>
-      </c>
-      <c r="L28" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" t="s">
-        <v>338</v>
-      </c>
-      <c r="N28" t="s">
-        <v>24</v>
-      </c>
-      <c r="O28" t="s">
-        <v>339</v>
-      </c>
-      <c r="P28" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5244,13 +5235,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -5261,58 +5252,58 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
         <v>344</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
         <v>345</v>
       </c>
-      <c r="E2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
         <v>346</v>
       </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
         <v>347</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
         <v>348</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>349</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>350</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>351</v>
       </c>
       <c r="R2">
         <v>21</v>
       </c>
       <c r="S2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -5323,13 +5314,13 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -5353,13 +5344,13 @@
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N3" t="s">
         <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P3" t="s">
         <v>24</v>
@@ -5371,10 +5362,10 @@
         <v>28</v>
       </c>
       <c r="S3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -5385,25 +5376,25 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
         <v>360</v>
-      </c>
-      <c r="D4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E4" t="s">
-        <v>360</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>362</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>363</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
@@ -5421,22 +5412,22 @@
         <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P4" t="s">
         <v>24</v>
       </c>
       <c r="Q4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="R4">
         <v>26</v>
       </c>
       <c r="S4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5447,58 +5438,58 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>366</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>353</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
         <v>367</v>
       </c>
-      <c r="D5" t="s">
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>354</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
         <v>368</v>
       </c>
-      <c r="E5" t="s">
-        <v>367</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
         <v>369</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>356</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>370</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>357</v>
-      </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="s">
-        <v>371</v>
-      </c>
-      <c r="P5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>372</v>
       </c>
       <c r="R5">
         <v>20</v>
       </c>
       <c r="S5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5506,22 +5497,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -5533,25 +5524,25 @@
         <v>24</v>
       </c>
       <c r="K6" t="s">
+        <v>373</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>374</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
+        <v>375</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
         <v>376</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" t="s">
-        <v>377</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" t="s">
-        <v>378</v>
-      </c>
-      <c r="P6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5559,52 +5550,52 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>379</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
         <v>380</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
         <v>381</v>
       </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
         <v>382</v>
       </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
         <v>383</v>
       </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
         <v>384</v>
-      </c>
-      <c r="L7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" t="s">
-        <v>385</v>
-      </c>
-      <c r="N7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" t="s">
-        <v>386</v>
-      </c>
-      <c r="P7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5612,52 +5603,52 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
         <v>388</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
         <v>389</v>
       </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
         <v>390</v>
       </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
         <v>391</v>
       </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
         <v>392</v>
-      </c>
-      <c r="L8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" t="s">
-        <v>393</v>
-      </c>
-      <c r="N8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" t="s">
-        <v>394</v>
-      </c>
-      <c r="P8" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5665,52 +5656,52 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
         <v>396</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>303</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
         <v>397</v>
       </c>
-      <c r="D9" t="s">
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>304</v>
+      </c>
+      <c r="N9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
         <v>398</v>
       </c>
-      <c r="E9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="s">
         <v>399</v>
-      </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
-        <v>305</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>400</v>
-      </c>
-      <c r="L9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" t="s">
-        <v>306</v>
-      </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
-        <v>401</v>
-      </c>
-      <c r="P9" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5721,58 +5712,58 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D10" t="s">
+        <v>401</v>
+      </c>
+      <c r="E10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
         <v>403</v>
       </c>
-      <c r="D10" t="s">
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
         <v>404</v>
       </c>
-      <c r="E10" t="s">
-        <v>403</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="L10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" t="s">
         <v>405</v>
       </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="N10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" t="s">
         <v>406</v>
       </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
         <v>407</v>
-      </c>
-      <c r="L10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" t="s">
-        <v>408</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" t="s">
-        <v>409</v>
-      </c>
-      <c r="P10" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>410</v>
       </c>
       <c r="R10">
         <v>21</v>
       </c>
       <c r="S10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5783,55 +5774,55 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>409</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>410</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
         <v>411</v>
       </c>
-      <c r="E11" t="s">
-        <v>411</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
         <v>412</v>
       </c>
-      <c r="H11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="N11" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" t="s">
+        <v>407</v>
+      </c>
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="s">
         <v>413</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>414</v>
-      </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>415</v>
-      </c>
-      <c r="N11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" t="s">
-        <v>410</v>
-      </c>
-      <c r="P11" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>416</v>
       </c>
       <c r="R11">
         <v>32</v>
       </c>
       <c r="S11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5842,58 +5833,58 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>414</v>
+      </c>
+      <c r="D12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" t="s">
+        <v>414</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>416</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
         <v>417</v>
       </c>
-      <c r="D12" t="s">
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
         <v>418</v>
       </c>
-      <c r="E12" t="s">
-        <v>417</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
         <v>419</v>
       </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="N12" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" t="s">
         <v>420</v>
       </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" t="s">
         <v>421</v>
-      </c>
-      <c r="L12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" t="s">
-        <v>422</v>
-      </c>
-      <c r="N12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O12" t="s">
-        <v>423</v>
-      </c>
-      <c r="P12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>424</v>
       </c>
       <c r="R12">
         <v>25</v>
       </c>
       <c r="S12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5904,58 +5895,58 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D13" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E13" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
       </c>
       <c r="G13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>403</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
+        <v>406</v>
+      </c>
+      <c r="N13" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" t="s">
         <v>407</v>
       </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" t="s">
-        <v>406</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>408</v>
-      </c>
-      <c r="L13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" t="s">
-        <v>409</v>
-      </c>
-      <c r="N13" t="s">
-        <v>24</v>
-      </c>
-      <c r="O13" t="s">
-        <v>410</v>
-      </c>
       <c r="P13" t="s">
         <v>24</v>
       </c>
       <c r="Q13" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="R13">
         <v>27</v>
       </c>
       <c r="S13" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T13" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5963,13 +5954,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E14" t="s">
         <v>153</v>
@@ -5978,37 +5969,37 @@
         <v>24</v>
       </c>
       <c r="G14" t="s">
+        <v>427</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>428</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>429</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
         <v>430</v>
       </c>
-      <c r="H14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="N14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
         <v>431</v>
       </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="s">
         <v>432</v>
-      </c>
-      <c r="L14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" t="s">
-        <v>433</v>
-      </c>
-      <c r="N14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" t="s">
-        <v>434</v>
-      </c>
-      <c r="P14" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -6016,13 +6007,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E15" t="s">
         <v>153</v>
@@ -6031,37 +6022,37 @@
         <v>24</v>
       </c>
       <c r="G15" t="s">
+        <v>435</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>437</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
         <v>438</v>
       </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" t="s">
         <v>439</v>
       </c>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="s">
         <v>440</v>
-      </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" t="s">
-        <v>441</v>
-      </c>
-      <c r="N15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O15" t="s">
-        <v>442</v>
-      </c>
-      <c r="P15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -6069,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E16" t="s">
         <v>153</v>
@@ -6084,37 +6075,37 @@
         <v>24</v>
       </c>
       <c r="G16" t="s">
+        <v>443</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>444</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
+        <v>445</v>
+      </c>
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
         <v>446</v>
       </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
         <v>447</v>
       </c>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="P16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="s">
         <v>448</v>
-      </c>
-      <c r="L16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" t="s">
-        <v>449</v>
-      </c>
-      <c r="N16" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" t="s">
-        <v>450</v>
-      </c>
-      <c r="P16" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -6122,52 +6113,52 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C17" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D17" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
+        <v>450</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>451</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>452</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
         <v>453</v>
       </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
         <v>454</v>
       </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
         <v>455</v>
       </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="P17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="s">
         <v>456</v>
-      </c>
-      <c r="L17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" t="s">
-        <v>457</v>
-      </c>
-      <c r="N17" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" t="s">
-        <v>458</v>
-      </c>
-      <c r="P17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -6175,13 +6166,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C18" t="s">
         <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E18" t="s">
         <v>143</v>
@@ -6228,13 +6219,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C19" t="s">
         <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E19" t="s">
         <v>159</v>
@@ -6281,13 +6272,13 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C20" t="s">
         <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E20" t="s">
         <v>168</v>
@@ -6302,7 +6293,7 @@
         <v>106</v>
       </c>
       <c r="I20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J20" t="s">
         <v>60</v>
@@ -6334,13 +6325,13 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C21" t="s">
         <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E21" t="s">
         <v>147</v>
@@ -6387,13 +6378,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C22" t="s">
         <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E22" t="s">
         <v>106</v>
@@ -6402,7 +6393,7 @@
         <v>106</v>
       </c>
       <c r="G22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
         <v>168</v>
@@ -6440,13 +6431,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C23" t="s">
         <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E23" t="s">
         <v>170</v>
@@ -6455,37 +6446,37 @@
         <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
       </c>
       <c r="I23" t="s">
+        <v>320</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>180</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
         <v>322</v>
       </c>
-      <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" t="s">
-        <v>181</v>
-      </c>
-      <c r="L23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" t="s">
-        <v>324</v>
-      </c>
       <c r="N23" t="s">
         <v>24</v>
       </c>
       <c r="O23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P23" t="s">
         <v>24</v>
       </c>
       <c r="Q23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -6493,13 +6484,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C24" t="s">
         <v>153</v>
       </c>
       <c r="D24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E24" t="s">
         <v>153</v>
@@ -6508,37 +6499,37 @@
         <v>24</v>
       </c>
       <c r="G24" t="s">
+        <v>471</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
+        <v>323</v>
+      </c>
+      <c r="J24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" t="s">
+        <v>321</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
+        <v>472</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" t="s">
+        <v>473</v>
+      </c>
+      <c r="P24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" t="s">
         <v>474</v>
-      </c>
-      <c r="H24" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" t="s">
-        <v>325</v>
-      </c>
-      <c r="J24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" t="s">
-        <v>323</v>
-      </c>
-      <c r="L24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" t="s">
-        <v>475</v>
-      </c>
-      <c r="N24" t="s">
-        <v>24</v>
-      </c>
-      <c r="O24" t="s">
-        <v>476</v>
-      </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -6546,13 +6537,13 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C25" t="s">
         <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -6561,25 +6552,25 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J25" t="s">
         <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="L25" t="s">
         <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N25" t="s">
         <v>24</v>
@@ -6591,7 +6582,7 @@
         <v>24</v>
       </c>
       <c r="Q25" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -6599,13 +6590,13 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
         <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E26" t="s">
         <v>170</v>
@@ -6626,7 +6617,7 @@
         <v>106</v>
       </c>
       <c r="K26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L26" t="s">
         <v>143</v>
@@ -6652,52 +6643,52 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
+        <v>480</v>
+      </c>
+      <c r="C27" t="s">
+        <v>481</v>
+      </c>
+      <c r="D27" t="s">
+        <v>482</v>
+      </c>
+      <c r="E27" t="s">
+        <v>481</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
         <v>483</v>
       </c>
-      <c r="C27" t="s">
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
         <v>484</v>
       </c>
-      <c r="D27" t="s">
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="s">
         <v>485</v>
       </c>
-      <c r="E27" t="s">
-        <v>484</v>
-      </c>
-      <c r="F27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
         <v>486</v>
       </c>
-      <c r="H27" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="N27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" t="s">
         <v>487</v>
       </c>
-      <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="P27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
         <v>488</v>
-      </c>
-      <c r="L27" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" t="s">
-        <v>489</v>
-      </c>
-      <c r="N27" t="s">
-        <v>24</v>
-      </c>
-      <c r="O27" t="s">
-        <v>490</v>
-      </c>
-      <c r="P27" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -6705,49 +6696,49 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C28" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E28" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F28" t="s">
         <v>24</v>
       </c>
       <c r="G28" t="s">
+        <v>489</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
+        <v>490</v>
+      </c>
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" t="s">
+        <v>491</v>
+      </c>
+      <c r="L28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" t="s">
         <v>492</v>
       </c>
-      <c r="H28" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="N28" t="s">
+        <v>24</v>
+      </c>
+      <c r="O28" t="s">
         <v>493</v>
       </c>
-      <c r="J28" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="P28" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="s">
         <v>494</v>
-      </c>
-      <c r="L28" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" t="s">
-        <v>495</v>
-      </c>
-      <c r="N28" t="s">
-        <v>24</v>
-      </c>
-      <c r="O28" t="s">
-        <v>496</v>
-      </c>
-      <c r="P28" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -6813,13 +6804,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -6830,55 +6821,55 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J2" t="s">
         <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="N2" t="s">
         <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P2" t="s">
         <v>24</v>
       </c>
       <c r="Q2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="R2">
         <v>32</v>
       </c>
       <c r="S2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="T2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -6889,58 +6880,58 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E3" t="s">
+        <v>499</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>411</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>501</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>412</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
         <v>502</v>
       </c>
-      <c r="D3" t="s">
-        <v>503</v>
-      </c>
-      <c r="E3" t="s">
-        <v>502</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
         <v>413</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>504</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>415</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="s">
-        <v>505</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>416</v>
       </c>
       <c r="R3">
         <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -6951,58 +6942,58 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D4" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
+        <v>418</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>417</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>416</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>419</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="s">
+        <v>420</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
         <v>421</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>420</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>419</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
-        <v>422</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" t="s">
-        <v>423</v>
-      </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>424</v>
       </c>
       <c r="R4">
         <v>29</v>
       </c>
       <c r="S4" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="T4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -7013,58 +7004,58 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
       </c>
       <c r="I5" t="s">
+        <v>417</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>418</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>416</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>419</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
         <v>420</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>421</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>419</v>
-      </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="s">
-        <v>422</v>
-      </c>
-      <c r="P5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>423</v>
       </c>
       <c r="R5">
         <v>31</v>
       </c>
       <c r="S5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -7072,13 +7063,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E6" t="s">
         <v>153</v>
@@ -7087,37 +7078,37 @@
         <v>24</v>
       </c>
       <c r="G6" t="s">
+        <v>511</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>512</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>513</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
         <v>514</v>
       </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
         <v>515</v>
       </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
         <v>516</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" t="s">
-        <v>517</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" t="s">
-        <v>518</v>
-      </c>
-      <c r="P6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -7125,13 +7116,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E7" t="s">
         <v>153</v>
@@ -7140,37 +7131,37 @@
         <v>24</v>
       </c>
       <c r="G7" t="s">
+        <v>519</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>521</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
         <v>522</v>
       </c>
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
         <v>523</v>
       </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
         <v>524</v>
-      </c>
-      <c r="L7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" t="s">
-        <v>525</v>
-      </c>
-      <c r="N7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" t="s">
-        <v>526</v>
-      </c>
-      <c r="P7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -7178,13 +7169,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E8" t="s">
         <v>153</v>
@@ -7193,37 +7184,37 @@
         <v>24</v>
       </c>
       <c r="G8" t="s">
+        <v>527</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>528</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>529</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
         <v>530</v>
       </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s">
         <v>531</v>
       </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
         <v>532</v>
-      </c>
-      <c r="L8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" t="s">
-        <v>533</v>
-      </c>
-      <c r="N8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" t="s">
-        <v>534</v>
-      </c>
-      <c r="P8" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -7231,52 +7222,52 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
         <v>76</v>
       </c>
       <c r="E9" t="s">
+        <v>450</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>451</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>452</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
         <v>453</v>
       </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
         <v>454</v>
       </c>
-      <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="N9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
         <v>455</v>
       </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="s">
         <v>456</v>
-      </c>
-      <c r="L9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" t="s">
-        <v>457</v>
-      </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
-        <v>458</v>
-      </c>
-      <c r="P9" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -7287,58 +7278,58 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L10" t="s">
         <v>24</v>
       </c>
       <c r="M10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N10" t="s">
         <v>24</v>
       </c>
       <c r="O10" t="s">
+        <v>262</v>
+      </c>
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
         <v>264</v>
-      </c>
-      <c r="P10" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>266</v>
       </c>
       <c r="R10">
         <v>31</v>
       </c>
       <c r="S10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="T10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -7349,58 +7340,58 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
+        <v>533</v>
+      </c>
+      <c r="D11" t="s">
+        <v>534</v>
+      </c>
+      <c r="E11" t="s">
+        <v>533</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>535</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>271</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>270</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>272</v>
+      </c>
+      <c r="N11" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" t="s">
         <v>536</v>
       </c>
-      <c r="D11" t="s">
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="s">
         <v>537</v>
-      </c>
-      <c r="E11" t="s">
-        <v>536</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>538</v>
-      </c>
-      <c r="H11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" t="s">
-        <v>273</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>272</v>
-      </c>
-      <c r="L11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" t="s">
-        <v>274</v>
-      </c>
-      <c r="N11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" t="s">
-        <v>539</v>
-      </c>
-      <c r="P11" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>540</v>
       </c>
       <c r="R11">
         <v>25</v>
       </c>
       <c r="S11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -7411,58 +7402,58 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
         <v>269</v>
       </c>
-      <c r="D12" t="s">
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
         <v>270</v>
       </c>
-      <c r="E12" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
         <v>271</v>
       </c>
-      <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
         <v>272</v>
       </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" t="s">
         <v>273</v>
       </c>
-      <c r="L12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" t="s">
         <v>274</v>
-      </c>
-      <c r="N12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O12" t="s">
-        <v>275</v>
-      </c>
-      <c r="P12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>276</v>
       </c>
       <c r="R12">
         <v>23</v>
       </c>
       <c r="S12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -7473,58 +7464,58 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
+        <v>538</v>
+      </c>
+      <c r="D13" t="s">
+        <v>539</v>
+      </c>
+      <c r="E13" t="s">
+        <v>538</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>271</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>270</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>540</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
+        <v>272</v>
+      </c>
+      <c r="N13" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" t="s">
+        <v>273</v>
+      </c>
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>535</v>
+      </c>
+      <c r="R13">
+        <v>24</v>
+      </c>
+      <c r="S13" t="s">
         <v>541</v>
       </c>
-      <c r="D13" t="s">
-        <v>542</v>
-      </c>
-      <c r="E13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" t="s">
-        <v>272</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>543</v>
-      </c>
-      <c r="L13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" t="s">
-        <v>274</v>
-      </c>
-      <c r="N13" t="s">
-        <v>24</v>
-      </c>
-      <c r="O13" t="s">
-        <v>275</v>
-      </c>
-      <c r="P13" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>538</v>
-      </c>
-      <c r="R13">
-        <v>24</v>
-      </c>
-      <c r="S13" t="s">
-        <v>544</v>
-      </c>
       <c r="T13" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -7532,13 +7523,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E14" t="s">
         <v>147</v>
@@ -7547,37 +7538,37 @@
         <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J14" t="s">
         <v>24</v>
       </c>
       <c r="K14" t="s">
+        <v>436</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
+        <v>435</v>
+      </c>
+      <c r="N14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
+        <v>544</v>
+      </c>
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="s">
         <v>439</v>
-      </c>
-      <c r="L14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" t="s">
-        <v>438</v>
-      </c>
-      <c r="N14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O14" t="s">
-        <v>547</v>
-      </c>
-      <c r="P14" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -7585,13 +7576,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E15" t="s">
         <v>147</v>
@@ -7600,37 +7591,37 @@
         <v>24</v>
       </c>
       <c r="G15" t="s">
+        <v>279</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>280</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
         <v>281</v>
       </c>
-      <c r="H15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
         <v>282</v>
       </c>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" t="s">
+        <v>245</v>
+      </c>
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="s">
         <v>283</v>
-      </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" t="s">
-        <v>284</v>
-      </c>
-      <c r="N15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O15" t="s">
-        <v>247</v>
-      </c>
-      <c r="P15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -7638,13 +7629,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E16" t="s">
         <v>147</v>
@@ -7653,37 +7644,37 @@
         <v>24</v>
       </c>
       <c r="G16" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>287</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
         <v>288</v>
       </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
         <v>289</v>
       </c>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
         <v>290</v>
       </c>
-      <c r="L16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="P16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="s">
         <v>291</v>
-      </c>
-      <c r="N16" t="s">
-        <v>24</v>
-      </c>
-      <c r="O16" t="s">
-        <v>292</v>
-      </c>
-      <c r="P16" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -7691,52 +7682,52 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D17" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
+        <v>301</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>302</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
         <v>303</v>
       </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
         <v>304</v>
       </c>
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
         <v>305</v>
       </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
         <v>306</v>
       </c>
-      <c r="L17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="P17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="s">
         <v>307</v>
-      </c>
-      <c r="N17" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" t="s">
-        <v>308</v>
-      </c>
-      <c r="P17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -7744,13 +7735,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C18" t="s">
         <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E18" t="s">
         <v>170</v>
@@ -7765,7 +7756,7 @@
         <v>106</v>
       </c>
       <c r="I18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J18" t="s">
         <v>149</v>
@@ -7797,13 +7788,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C19" t="s">
         <v>153</v>
       </c>
       <c r="D19" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E19" t="s">
         <v>149</v>
@@ -7850,13 +7841,13 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C20" t="s">
         <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E20" t="s">
         <v>163</v>
@@ -7903,13 +7894,13 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
         <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E21" t="s">
         <v>60</v>
@@ -7930,7 +7921,7 @@
         <v>106</v>
       </c>
       <c r="K21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s">
         <v>155</v>
@@ -7956,13 +7947,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C22" t="s">
         <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E22" t="s">
         <v>106</v>
@@ -7971,7 +7962,7 @@
         <v>106</v>
       </c>
       <c r="G22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
         <v>157</v>
@@ -8006,16 +7997,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C23" t="s">
         <v>153</v>
       </c>
       <c r="D23" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E23" t="s">
         <v>153</v>
@@ -8024,51 +8015,51 @@
         <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
       </c>
       <c r="I23" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J23" t="s">
         <v>24</v>
       </c>
       <c r="K23" t="s">
+        <v>471</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
+        <v>551</v>
+      </c>
+      <c r="N23" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" t="s">
+        <v>473</v>
+      </c>
+      <c r="P23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="s">
         <v>474</v>
-      </c>
-      <c r="L23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" t="s">
-        <v>554</v>
-      </c>
-      <c r="N23" t="s">
-        <v>24</v>
-      </c>
-      <c r="O23" t="s">
-        <v>476</v>
-      </c>
-      <c r="P23" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C24" t="s">
         <v>147</v>
       </c>
       <c r="D24" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E24" t="s">
         <v>147</v>
@@ -8077,37 +8068,37 @@
         <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
       </c>
       <c r="I24" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
       </c>
       <c r="K24" t="s">
+        <v>321</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
+        <v>180</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" t="s">
+        <v>181</v>
+      </c>
+      <c r="P24" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" t="s">
         <v>323</v>
-      </c>
-      <c r="L24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" t="s">
-        <v>181</v>
-      </c>
-      <c r="N24" t="s">
-        <v>24</v>
-      </c>
-      <c r="O24" t="s">
-        <v>182</v>
-      </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -8115,13 +8106,13 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C25" t="s">
         <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -8130,25 +8121,25 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J25" t="s">
         <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L25" t="s">
         <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N25" t="s">
         <v>24</v>
@@ -8162,13 +8153,13 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E26" t="s">
         <v>24</v>
@@ -8191,49 +8182,49 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C27" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E27" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
       </c>
       <c r="G27" t="s">
+        <v>557</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>558</v>
+      </c>
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="s">
+        <v>559</v>
+      </c>
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
         <v>560</v>
       </c>
-      <c r="H27" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="N27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" t="s">
         <v>561</v>
       </c>
-      <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="P27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
         <v>562</v>
-      </c>
-      <c r="L27" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" t="s">
-        <v>563</v>
-      </c>
-      <c r="N27" t="s">
-        <v>24</v>
-      </c>
-      <c r="O27" t="s">
-        <v>564</v>
-      </c>
-      <c r="P27" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>565</v>
       </c>
     </row>
   </sheetData>
